--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.45159683309245</v>
+        <v>14.37338448537752</v>
       </c>
       <c r="D2" t="n">
-        <v>88.45007965730551</v>
+        <v>14.37313794431214</v>
       </c>
       <c r="E2" t="n">
-        <v>5.482127944412035</v>
+        <v>0.8908457909669556</v>
       </c>
       <c r="F2" t="n">
-        <v>5.48902711240634</v>
+        <v>0.8919669057660302</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.48734094426838</v>
+        <v>12.59169290344361</v>
       </c>
       <c r="D3" t="n">
-        <v>77.47202543249283</v>
+        <v>12.58920413278008</v>
       </c>
       <c r="E3" t="n">
-        <v>5.482127944412035</v>
+        <v>0.8908457909669556</v>
       </c>
       <c r="F3" t="n">
-        <v>5.48902711240634</v>
+        <v>0.8919669057660302</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
